--- a/artfynd/A 33503-2023 artfynd.xlsx
+++ b/artfynd/A 33503-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33503-2023 artfynd.xlsx
+++ b/artfynd/A 33503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Utter barmarksinventering RMÖ/GDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123719322</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56330</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N.Ådalen (Y454), Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>609647</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6958697</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Y454</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Peter Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Peter Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>

--- a/artfynd/A 33503-2023 artfynd.xlsx
+++ b/artfynd/A 33503-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>123719322</v>
       </c>
       <c r="B3" t="n">
-        <v>56330</v>
+        <v>56333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33503-2023 artfynd.xlsx
+++ b/artfynd/A 33503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,117 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Utter barmarksinventering RMÖ/GDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>123719322</v>
-      </c>
-      <c r="B3" t="n">
-        <v>56333</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100077</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>N.Ådalen (Y454), Mpd</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>609647</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6958697</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ljustorp</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Y454</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Peter Nilsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Peter Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>

--- a/artfynd/A 33503-2023 artfynd.xlsx
+++ b/artfynd/A 33503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107264490</v>
+        <v>119613354</v>
       </c>
       <c r="B2" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100077</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N.Ådalen (Y454), Mpd</t>
+          <t>Nedre Ådalen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609646.9182507963</v>
+        <v>609546</v>
       </c>
       <c r="R2" t="n">
-        <v>6958697.204953351</v>
+        <v>6958888</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,29 +741,14 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Y454</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,21 +757,255 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119613350</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92605</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>898</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nedre Ådalen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>609486</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6958847</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>107264490</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N.Ådalen (Y454), Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>609647</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6958697</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Y454</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-09-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Peter Nilsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>David Bystedt, Frans Olofsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>

--- a/artfynd/A 33503-2023 artfynd.xlsx
+++ b/artfynd/A 33503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119613354</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119613350</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,8 +1025,18 @@
           <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107264490</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>